--- a/artfynd/S 2398-2022 artfynd.xlsx
+++ b/artfynd/S 2398-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,62 +918,52 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62756539</v>
+        <v>136821037</v>
       </c>
       <c r="B4" t="n">
-        <v>104132</v>
+        <v>58169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1910</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärglin</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Radiola linoides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Roth</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strutbackarna. 200 m NV om, Vrm</t>
+          <t>Billingsmossarna, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455910</v>
+        <v>458561</v>
       </c>
       <c r="R4" t="n">
-        <v>6557270</v>
+        <v>6557333</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,24 +985,14 @@
           <t>Visnum</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>S-Kri-0219</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-09-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>I vägens mittsträng, Längs båda vägkanterna,</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,28 +1004,154 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>skogsbilväg</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Lundqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136821037</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>62756539</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104132</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärglin</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Radiola linoides</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Roth</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Strutbackarna. 200 m NV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>455910</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6557270</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Visnum</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>S-Kri-0219</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2016-08-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2016-09-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I vägens mittsträng, Längs båda vägkanterna,</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>skogsbilväg</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Owe Nilsson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Olof Rosenqvist</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/62756539</t>
         </is>
@@ -1056,6 +1162,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2398-2022 artfynd.xlsx
+++ b/artfynd/S 2398-2022 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136821037</v>
       </c>
       <c r="B4" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2398-2022 artfynd.xlsx
+++ b/artfynd/S 2398-2022 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136821037</v>
       </c>
       <c r="B4" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2398-2022 artfynd.xlsx
+++ b/artfynd/S 2398-2022 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136821037</v>
       </c>
       <c r="B4" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2398-2022 artfynd.xlsx
+++ b/artfynd/S 2398-2022 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136821037</v>
       </c>
       <c r="B4" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2398-2022 artfynd.xlsx
+++ b/artfynd/S 2398-2022 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136821037</v>
       </c>
       <c r="B4" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
